--- a/data/多人群画像_模板_3.0.xlsx
+++ b/data/多人群画像_模板_3.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://insidemedia-my.sharepoint.com/personal/sylas_xia_wppmedia_com/Documents/桌面/常用工具/画像3.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BCCE28AAF4C3BA3E9668B6BCE990CE6A10E87B89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCCF9ADC-3B0B-421A-BCD9-9CDFC71FCFF0}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_BCCE28AAF4C3BA3E9668B6BCE990CE6A10E87B89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E69C485C-427D-49E9-85FE-E70E0E31C636}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3" sheetId="1" r:id="rId1"/>
@@ -2096,46 +2096,28 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2147,6 +2129,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2272,11 +2272,9 @@
   <autoFilter ref="A5:A214" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="彩妆功效需求"/>
         <filter val="彩妆年消费金额"/>
         <filter val="彩妆年消费频次"/>
         <filter val="策略人群"/>
-        <filter val="策略人群3.0"/>
         <filter val="购买者年龄分布"/>
         <filter val="购买者所处城市等级"/>
         <filter val="护肤年消费金额"/>
@@ -2601,17 +2599,17 @@
   <sheetData>
     <row r="2" spans="1:12" ht="14.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B3" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="70" t="s">
+      <c r="B3" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="64" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:12" s="31" customFormat="1" ht="14.5" customHeight="1" thickBot="1">
       <c r="A4" s="42"/>
-      <c r="B4" s="63"/>
+      <c r="B4" s="49"/>
       <c r="C4" s="59"/>
       <c r="D4" s="40" t="str">
         <f>'1'!B1</f>
@@ -2654,10 +2652,10 @@
       <c r="A5" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="69"/>
+      <c r="C5" s="63"/>
       <c r="D5" s="41">
         <f>'1'!B2</f>
         <v>42410</v>
@@ -2699,7 +2697,7 @@
       <c r="A6" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="66" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
@@ -2746,7 +2744,7 @@
       <c r="A7" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="49"/>
+      <c r="B7" s="56"/>
       <c r="C7" s="15" t="s">
         <v>6</v>
       </c>
@@ -2791,7 +2789,7 @@
       <c r="A8" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="50"/>
+      <c r="B8" s="57"/>
       <c r="C8" s="15" t="s">
         <v>7</v>
       </c>
@@ -2883,7 +2881,7 @@
       <c r="A10" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="49"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="18" t="s">
         <v>10</v>
       </c>
@@ -2928,7 +2926,7 @@
       <c r="A11" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="49"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="18" t="s">
         <v>11</v>
       </c>
@@ -2973,7 +2971,7 @@
       <c r="A12" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="49"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="18" t="s">
         <v>12</v>
       </c>
@@ -3018,7 +3016,7 @@
       <c r="A13" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="49"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="18" t="s">
         <v>13</v>
       </c>
@@ -3063,7 +3061,7 @@
       <c r="A14" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="49"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="18" t="s">
         <v>14</v>
       </c>
@@ -3108,7 +3106,7 @@
       <c r="A15" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="49"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="18" t="s">
         <v>15</v>
       </c>
@@ -3153,7 +3151,7 @@
       <c r="A16" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="50"/>
+      <c r="B16" s="57"/>
       <c r="C16" s="18" t="s">
         <v>16</v>
       </c>
@@ -3198,7 +3196,7 @@
       <c r="A17" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="69" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="13" t="s">
@@ -3245,7 +3243,7 @@
       <c r="A18" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="49"/>
+      <c r="B18" s="56"/>
       <c r="C18" s="15" t="s">
         <v>19</v>
       </c>
@@ -3290,7 +3288,7 @@
       <c r="A19" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="49"/>
+      <c r="B19" s="56"/>
       <c r="C19" s="15" t="s">
         <v>20</v>
       </c>
@@ -3335,7 +3333,7 @@
       <c r="A20" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="49"/>
+      <c r="B20" s="56"/>
       <c r="C20" s="15" t="s">
         <v>21</v>
       </c>
@@ -3380,7 +3378,7 @@
       <c r="A21" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="49"/>
+      <c r="B21" s="56"/>
       <c r="C21" s="15" t="s">
         <v>22</v>
       </c>
@@ -3425,7 +3423,7 @@
       <c r="A22" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="49"/>
+      <c r="B22" s="56"/>
       <c r="C22" s="15" t="s">
         <v>23</v>
       </c>
@@ -3470,7 +3468,7 @@
       <c r="A23" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="50"/>
+      <c r="B23" s="57"/>
       <c r="C23" s="15" t="s">
         <v>24</v>
       </c>
@@ -3515,7 +3513,7 @@
       <c r="A24" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="67" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="20">
@@ -3562,7 +3560,7 @@
       <c r="A25" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="49"/>
+      <c r="B25" s="56"/>
       <c r="C25" s="18">
         <v>2</v>
       </c>
@@ -3607,7 +3605,7 @@
       <c r="A26" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="49"/>
+      <c r="B26" s="56"/>
       <c r="C26" s="18">
         <v>3</v>
       </c>
@@ -3652,7 +3650,7 @@
       <c r="A27" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="49"/>
+      <c r="B27" s="56"/>
       <c r="C27" s="18">
         <v>4</v>
       </c>
@@ -3697,7 +3695,7 @@
       <c r="A28" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="49"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="18">
         <v>5</v>
       </c>
@@ -3742,7 +3740,7 @@
       <c r="A29" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="50"/>
+      <c r="B29" s="57"/>
       <c r="C29" s="18" t="s">
         <v>26</v>
       </c>
@@ -3834,7 +3832,7 @@
       <c r="A31" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="49"/>
+      <c r="B31" s="56"/>
       <c r="C31" s="15" t="s">
         <v>29</v>
       </c>
@@ -3879,7 +3877,7 @@
       <c r="A32" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="49"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="15" t="s">
         <v>30</v>
       </c>
@@ -3924,7 +3922,7 @@
       <c r="A33" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="49"/>
+      <c r="B33" s="56"/>
       <c r="C33" s="15" t="s">
         <v>31</v>
       </c>
@@ -3969,7 +3967,7 @@
       <c r="A34" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="50"/>
+      <c r="B34" s="57"/>
       <c r="C34" s="15" t="s">
         <v>32</v>
       </c>
@@ -4061,7 +4059,7 @@
       <c r="A36" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="49"/>
+      <c r="B36" s="56"/>
       <c r="C36" s="18" t="s">
         <v>35</v>
       </c>
@@ -4106,7 +4104,7 @@
       <c r="A37" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B37" s="49"/>
+      <c r="B37" s="56"/>
       <c r="C37" s="18" t="s">
         <v>36</v>
       </c>
@@ -4151,7 +4149,7 @@
       <c r="A38" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="50"/>
+      <c r="B38" s="57"/>
       <c r="C38" s="18" t="s">
         <v>37</v>
       </c>
@@ -4243,7 +4241,7 @@
       <c r="A40" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="49"/>
+      <c r="B40" s="56"/>
       <c r="C40" s="15" t="s">
         <v>40</v>
       </c>
@@ -4288,7 +4286,7 @@
       <c r="A41" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="49"/>
+      <c r="B41" s="56"/>
       <c r="C41" s="15" t="s">
         <v>41</v>
       </c>
@@ -4333,7 +4331,7 @@
       <c r="A42" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="49"/>
+      <c r="B42" s="56"/>
       <c r="C42" s="15" t="s">
         <v>42</v>
       </c>
@@ -4378,7 +4376,7 @@
       <c r="A43" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="49"/>
+      <c r="B43" s="56"/>
       <c r="C43" s="15" t="s">
         <v>43</v>
       </c>
@@ -4423,7 +4421,7 @@
       <c r="A44" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="50"/>
+      <c r="B44" s="57"/>
       <c r="C44" s="15" t="s">
         <v>44</v>
       </c>
@@ -4515,7 +4513,7 @@
       <c r="A46" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="49"/>
+      <c r="B46" s="56"/>
       <c r="C46" s="18" t="s">
         <v>35</v>
       </c>
@@ -4560,7 +4558,7 @@
       <c r="A47" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="49"/>
+      <c r="B47" s="56"/>
       <c r="C47" s="18" t="s">
         <v>36</v>
       </c>
@@ -4605,7 +4603,7 @@
       <c r="A48" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="50"/>
+      <c r="B48" s="57"/>
       <c r="C48" s="18" t="s">
         <v>37</v>
       </c>
@@ -4650,7 +4648,7 @@
       <c r="A49" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="66" t="s">
+      <c r="B49" s="60" t="s">
         <v>46</v>
       </c>
       <c r="C49" s="20" t="s">
@@ -4697,7 +4695,7 @@
       <c r="A50" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="49"/>
+      <c r="B50" s="56"/>
       <c r="C50" s="18" t="s">
         <v>48</v>
       </c>
@@ -4742,7 +4740,7 @@
       <c r="A51" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="49"/>
+      <c r="B51" s="56"/>
       <c r="C51" s="18" t="s">
         <v>49</v>
       </c>
@@ -4787,7 +4785,7 @@
       <c r="A52" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B52" s="49"/>
+      <c r="B52" s="56"/>
       <c r="C52" s="18" t="s">
         <v>50</v>
       </c>
@@ -4832,7 +4830,7 @@
       <c r="A53" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B53" s="49"/>
+      <c r="B53" s="56"/>
       <c r="C53" s="18" t="s">
         <v>51</v>
       </c>
@@ -4877,7 +4875,7 @@
       <c r="A54" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="49"/>
+      <c r="B54" s="56"/>
       <c r="C54" s="18" t="s">
         <v>52</v>
       </c>
@@ -4922,7 +4920,7 @@
       <c r="A55" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="49"/>
+      <c r="B55" s="56"/>
       <c r="C55" s="18" t="s">
         <v>53</v>
       </c>
@@ -4967,7 +4965,7 @@
       <c r="A56" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B56" s="49"/>
+      <c r="B56" s="56"/>
       <c r="C56" s="18" t="s">
         <v>54</v>
       </c>
@@ -5012,7 +5010,7 @@
       <c r="A57" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="49"/>
+      <c r="B57" s="56"/>
       <c r="C57" s="18" t="s">
         <v>55</v>
       </c>
@@ -5053,11 +5051,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
+    <row r="58" spans="1:12" ht="14.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A58" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="54" t="s">
+      <c r="B58" s="67" t="s">
         <v>56</v>
       </c>
       <c r="C58" s="22" t="s">
@@ -5100,11 +5098,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="14.5" customHeight="1">
+    <row r="59" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A59" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B59" s="49"/>
+      <c r="B59" s="56"/>
       <c r="C59" s="29" t="s">
         <v>58</v>
       </c>
@@ -5145,11 +5143,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="14.5" customHeight="1">
+    <row r="60" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A60" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="49"/>
+      <c r="B60" s="56"/>
       <c r="C60" s="29" t="s">
         <v>59</v>
       </c>
@@ -5190,11 +5188,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="14.5" customHeight="1">
+    <row r="61" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A61" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="49"/>
+      <c r="B61" s="56"/>
       <c r="C61" s="29" t="s">
         <v>60</v>
       </c>
@@ -5235,11 +5233,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="14.5" customHeight="1">
+    <row r="62" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A62" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="49"/>
+      <c r="B62" s="56"/>
       <c r="C62" s="29" t="s">
         <v>61</v>
       </c>
@@ -5280,11 +5278,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="14.5" customHeight="1">
+    <row r="63" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A63" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B63" s="49"/>
+      <c r="B63" s="56"/>
       <c r="C63" s="29" t="s">
         <v>62</v>
       </c>
@@ -5325,11 +5323,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="14.5" customHeight="1">
+    <row r="64" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A64" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B64" s="49"/>
+      <c r="B64" s="56"/>
       <c r="C64" s="29" t="s">
         <v>63</v>
       </c>
@@ -5370,11 +5368,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="14.5" customHeight="1">
+    <row r="65" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A65" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B65" s="49"/>
+      <c r="B65" s="56"/>
       <c r="C65" s="29" t="s">
         <v>64</v>
       </c>
@@ -5415,11 +5413,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="14.5" customHeight="1">
+    <row r="66" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A66" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B66" s="49"/>
+      <c r="B66" s="56"/>
       <c r="C66" s="29" t="s">
         <v>65</v>
       </c>
@@ -5460,11 +5458,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
+    <row r="67" spans="1:12" ht="14.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A67" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B67" s="50"/>
+      <c r="B67" s="57"/>
       <c r="C67" s="30" t="s">
         <v>66</v>
       </c>
@@ -5556,7 +5554,7 @@
       <c r="A69" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="49"/>
+      <c r="B69" s="56"/>
       <c r="C69" s="33" t="s">
         <v>69</v>
       </c>
@@ -5601,7 +5599,7 @@
       <c r="A70" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B70" s="49"/>
+      <c r="B70" s="56"/>
       <c r="C70" s="33" t="s">
         <v>29</v>
       </c>
@@ -5646,7 +5644,7 @@
       <c r="A71" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="49"/>
+      <c r="B71" s="56"/>
       <c r="C71" s="33" t="s">
         <v>30</v>
       </c>
@@ -5691,7 +5689,7 @@
       <c r="A72" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="49"/>
+      <c r="B72" s="56"/>
       <c r="C72" s="33" t="s">
         <v>70</v>
       </c>
@@ -5736,7 +5734,7 @@
       <c r="A73" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B73" s="49"/>
+      <c r="B73" s="56"/>
       <c r="C73" s="33" t="s">
         <v>71</v>
       </c>
@@ -5781,7 +5779,7 @@
       <c r="A74" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="49"/>
+      <c r="B74" s="56"/>
       <c r="C74" s="33" t="s">
         <v>72</v>
       </c>
@@ -5826,7 +5824,7 @@
       <c r="A75" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="50"/>
+      <c r="B75" s="57"/>
       <c r="C75" s="34" t="s">
         <v>73</v>
       </c>
@@ -5918,7 +5916,7 @@
       <c r="A77" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B77" s="49"/>
+      <c r="B77" s="56"/>
       <c r="C77" s="33" t="s">
         <v>76</v>
       </c>
@@ -5963,7 +5961,7 @@
       <c r="A78" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B78" s="49"/>
+      <c r="B78" s="56"/>
       <c r="C78" s="33" t="s">
         <v>77</v>
       </c>
@@ -6008,7 +6006,7 @@
       <c r="A79" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B79" s="49"/>
+      <c r="B79" s="56"/>
       <c r="C79" s="33" t="s">
         <v>78</v>
       </c>
@@ -6053,7 +6051,7 @@
       <c r="A80" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B80" s="49"/>
+      <c r="B80" s="56"/>
       <c r="C80" s="33" t="s">
         <v>79</v>
       </c>
@@ -6098,7 +6096,7 @@
       <c r="A81" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B81" s="49"/>
+      <c r="B81" s="56"/>
       <c r="C81" s="33" t="s">
         <v>80</v>
       </c>
@@ -6143,7 +6141,7 @@
       <c r="A82" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B82" s="49"/>
+      <c r="B82" s="56"/>
       <c r="C82" s="33" t="s">
         <v>81</v>
       </c>
@@ -6188,7 +6186,7 @@
       <c r="A83" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B83" s="49"/>
+      <c r="B83" s="56"/>
       <c r="C83" s="33" t="s">
         <v>82</v>
       </c>
@@ -6233,7 +6231,7 @@
       <c r="A84" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B84" s="49"/>
+      <c r="B84" s="56"/>
       <c r="C84" s="33" t="s">
         <v>83</v>
       </c>
@@ -6278,7 +6276,7 @@
       <c r="A85" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B85" s="49"/>
+      <c r="B85" s="56"/>
       <c r="C85" s="33" t="s">
         <v>84</v>
       </c>
@@ -6323,7 +6321,7 @@
       <c r="A86" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B86" s="50"/>
+      <c r="B86" s="57"/>
       <c r="C86" s="34" t="s">
         <v>85</v>
       </c>
@@ -6368,7 +6366,7 @@
       <c r="A87" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="61" t="s">
+      <c r="B87" s="65" t="s">
         <v>86</v>
       </c>
       <c r="C87" s="36" t="s">
@@ -6415,7 +6413,7 @@
       <c r="A88" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="49"/>
+      <c r="B88" s="56"/>
       <c r="C88" s="33" t="s">
         <v>88</v>
       </c>
@@ -6460,7 +6458,7 @@
       <c r="A89" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="B89" s="49"/>
+      <c r="B89" s="56"/>
       <c r="C89" s="33" t="s">
         <v>89</v>
       </c>
@@ -6505,7 +6503,7 @@
       <c r="A90" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="B90" s="49"/>
+      <c r="B90" s="56"/>
       <c r="C90" s="33" t="s">
         <v>90</v>
       </c>
@@ -6550,7 +6548,7 @@
       <c r="A91" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="B91" s="49"/>
+      <c r="B91" s="56"/>
       <c r="C91" s="35" t="s">
         <v>85</v>
       </c>
@@ -6642,7 +6640,7 @@
       <c r="A93" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="B93" s="49"/>
+      <c r="B93" s="56"/>
       <c r="C93" s="33" t="s">
         <v>93</v>
       </c>
@@ -6687,7 +6685,7 @@
       <c r="A94" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="B94" s="49"/>
+      <c r="B94" s="56"/>
       <c r="C94" s="33" t="s">
         <v>94</v>
       </c>
@@ -6732,7 +6730,7 @@
       <c r="A95" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="B95" s="49"/>
+      <c r="B95" s="56"/>
       <c r="C95" s="33" t="s">
         <v>95</v>
       </c>
@@ -6777,7 +6775,7 @@
       <c r="A96" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="B96" s="50"/>
+      <c r="B96" s="57"/>
       <c r="C96" s="34" t="s">
         <v>85</v>
       </c>
@@ -6869,7 +6867,7 @@
       <c r="A98" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="B98" s="49"/>
+      <c r="B98" s="56"/>
       <c r="C98" s="33" t="s">
         <v>98</v>
       </c>
@@ -6914,7 +6912,7 @@
       <c r="A99" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="B99" s="49"/>
+      <c r="B99" s="56"/>
       <c r="C99" s="33" t="s">
         <v>99</v>
       </c>
@@ -6959,7 +6957,7 @@
       <c r="A100" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="B100" s="49"/>
+      <c r="B100" s="56"/>
       <c r="C100" s="33" t="s">
         <v>100</v>
       </c>
@@ -7004,7 +7002,7 @@
       <c r="A101" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="B101" s="49"/>
+      <c r="B101" s="56"/>
       <c r="C101" s="33" t="s">
         <v>101</v>
       </c>
@@ -7049,7 +7047,7 @@
       <c r="A102" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="B102" s="50"/>
+      <c r="B102" s="57"/>
       <c r="C102" s="34" t="s">
         <v>85</v>
       </c>
@@ -7141,7 +7139,7 @@
       <c r="A104" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="B104" s="49"/>
+      <c r="B104" s="56"/>
       <c r="C104" s="33" t="s">
         <v>104</v>
       </c>
@@ -7186,7 +7184,7 @@
       <c r="A105" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="B105" s="49"/>
+      <c r="B105" s="56"/>
       <c r="C105" s="33" t="s">
         <v>105</v>
       </c>
@@ -7231,7 +7229,7 @@
       <c r="A106" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="B106" s="49"/>
+      <c r="B106" s="56"/>
       <c r="C106" s="33" t="s">
         <v>106</v>
       </c>
@@ -7276,7 +7274,7 @@
       <c r="A107" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="B107" s="49"/>
+      <c r="B107" s="56"/>
       <c r="C107" s="33" t="s">
         <v>107</v>
       </c>
@@ -7321,7 +7319,7 @@
       <c r="A108" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="B108" s="49"/>
+      <c r="B108" s="56"/>
       <c r="C108" s="33" t="s">
         <v>108</v>
       </c>
@@ -7366,7 +7364,7 @@
       <c r="A109" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="B109" s="49"/>
+      <c r="B109" s="56"/>
       <c r="C109" s="33" t="s">
         <v>109</v>
       </c>
@@ -7411,7 +7409,7 @@
       <c r="A110" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="B110" s="50"/>
+      <c r="B110" s="57"/>
       <c r="C110" s="34" t="s">
         <v>85</v>
       </c>
@@ -7503,7 +7501,7 @@
       <c r="A112" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B112" s="49"/>
+      <c r="B112" s="56"/>
       <c r="C112" s="33" t="s">
         <v>112</v>
       </c>
@@ -7548,7 +7546,7 @@
       <c r="A113" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B113" s="49"/>
+      <c r="B113" s="56"/>
       <c r="C113" s="33" t="s">
         <v>113</v>
       </c>
@@ -7593,7 +7591,7 @@
       <c r="A114" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B114" s="49"/>
+      <c r="B114" s="56"/>
       <c r="C114" s="33" t="s">
         <v>114</v>
       </c>
@@ -7638,7 +7636,7 @@
       <c r="A115" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B115" s="49"/>
+      <c r="B115" s="56"/>
       <c r="C115" s="33" t="s">
         <v>115</v>
       </c>
@@ -7683,7 +7681,7 @@
       <c r="A116" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B116" s="49"/>
+      <c r="B116" s="56"/>
       <c r="C116" s="33" t="s">
         <v>116</v>
       </c>
@@ -7728,7 +7726,7 @@
       <c r="A117" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B117" s="49"/>
+      <c r="B117" s="56"/>
       <c r="C117" s="33" t="s">
         <v>117</v>
       </c>
@@ -7773,7 +7771,7 @@
       <c r="A118" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B118" s="49"/>
+      <c r="B118" s="56"/>
       <c r="C118" s="33" t="s">
         <v>118</v>
       </c>
@@ -7818,7 +7816,7 @@
       <c r="A119" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B119" s="49"/>
+      <c r="B119" s="56"/>
       <c r="C119" s="33" t="s">
         <v>119</v>
       </c>
@@ -7863,7 +7861,7 @@
       <c r="A120" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B120" s="49"/>
+      <c r="B120" s="56"/>
       <c r="C120" s="33" t="s">
         <v>120</v>
       </c>
@@ -7908,7 +7906,7 @@
       <c r="A121" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B121" s="49"/>
+      <c r="B121" s="56"/>
       <c r="C121" s="33" t="s">
         <v>121</v>
       </c>
@@ -7953,7 +7951,7 @@
       <c r="A122" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B122" s="49"/>
+      <c r="B122" s="56"/>
       <c r="C122" s="33" t="s">
         <v>122</v>
       </c>
@@ -7998,7 +7996,7 @@
       <c r="A123" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B123" s="49"/>
+      <c r="B123" s="56"/>
       <c r="C123" s="33" t="s">
         <v>123</v>
       </c>
@@ -8043,7 +8041,7 @@
       <c r="A124" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B124" s="49"/>
+      <c r="B124" s="56"/>
       <c r="C124" s="33" t="s">
         <v>124</v>
       </c>
@@ -8088,7 +8086,7 @@
       <c r="A125" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B125" s="49"/>
+      <c r="B125" s="56"/>
       <c r="C125" s="33" t="s">
         <v>125</v>
       </c>
@@ -8133,7 +8131,7 @@
       <c r="A126" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B126" s="49"/>
+      <c r="B126" s="56"/>
       <c r="C126" s="33" t="s">
         <v>126</v>
       </c>
@@ -8178,7 +8176,7 @@
       <c r="A127" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="B127" s="49"/>
+      <c r="B127" s="56"/>
       <c r="C127" s="33" t="s">
         <v>127</v>
       </c>
@@ -8315,7 +8313,7 @@
       <c r="A130" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B130" s="49"/>
+      <c r="B130" s="56"/>
       <c r="C130" s="33" t="s">
         <v>131</v>
       </c>
@@ -8360,7 +8358,7 @@
       <c r="A131" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B131" s="49"/>
+      <c r="B131" s="56"/>
       <c r="C131" s="33" t="s">
         <v>119</v>
       </c>
@@ -8405,7 +8403,7 @@
       <c r="A132" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B132" s="49"/>
+      <c r="B132" s="56"/>
       <c r="C132" s="33" t="s">
         <v>132</v>
       </c>
@@ -8450,7 +8448,7 @@
       <c r="A133" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B133" s="49"/>
+      <c r="B133" s="56"/>
       <c r="C133" s="33" t="s">
         <v>133</v>
       </c>
@@ -8495,7 +8493,7 @@
       <c r="A134" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B134" s="49"/>
+      <c r="B134" s="56"/>
       <c r="C134" s="33" t="s">
         <v>134</v>
       </c>
@@ -8581,7 +8579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
+    <row r="136" spans="1:12" ht="14.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A136" s="42" t="s">
         <v>136</v>
       </c>
@@ -8628,11 +8626,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="14.5" customHeight="1">
+    <row r="137" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A137" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B137" s="49"/>
+      <c r="B137" s="56"/>
       <c r="C137" s="33" t="s">
         <v>114</v>
       </c>
@@ -8673,11 +8671,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="14.5" customHeight="1">
+    <row r="138" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A138" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B138" s="49"/>
+      <c r="B138" s="56"/>
       <c r="C138" s="33" t="s">
         <v>138</v>
       </c>
@@ -8718,11 +8716,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="14.5" customHeight="1">
+    <row r="139" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A139" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B139" s="49"/>
+      <c r="B139" s="56"/>
       <c r="C139" s="33" t="s">
         <v>139</v>
       </c>
@@ -8763,11 +8761,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="14.5" customHeight="1">
+    <row r="140" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A140" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B140" s="49"/>
+      <c r="B140" s="56"/>
       <c r="C140" s="33" t="s">
         <v>140</v>
       </c>
@@ -8808,11 +8806,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="14.5" customHeight="1">
+    <row r="141" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A141" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B141" s="49"/>
+      <c r="B141" s="56"/>
       <c r="C141" s="33" t="s">
         <v>141</v>
       </c>
@@ -8853,11 +8851,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="14.5" customHeight="1">
+    <row r="142" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A142" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B142" s="49"/>
+      <c r="B142" s="56"/>
       <c r="C142" s="33" t="s">
         <v>142</v>
       </c>
@@ -8898,11 +8896,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="14.5" customHeight="1">
+    <row r="143" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A143" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B143" s="49"/>
+      <c r="B143" s="56"/>
       <c r="C143" s="33" t="s">
         <v>143</v>
       </c>
@@ -8943,11 +8941,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="14.5" customHeight="1">
+    <row r="144" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A144" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B144" s="49"/>
+      <c r="B144" s="56"/>
       <c r="C144" s="33" t="s">
         <v>144</v>
       </c>
@@ -8988,11 +8986,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="14.5" customHeight="1">
+    <row r="145" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A145" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B145" s="49"/>
+      <c r="B145" s="56"/>
       <c r="C145" s="33" t="s">
         <v>115</v>
       </c>
@@ -9033,11 +9031,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="14.5" customHeight="1">
+    <row r="146" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A146" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B146" s="49"/>
+      <c r="B146" s="56"/>
       <c r="C146" s="33" t="s">
         <v>145</v>
       </c>
@@ -9078,11 +9076,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="14.5" customHeight="1">
+    <row r="147" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A147" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B147" s="49"/>
+      <c r="B147" s="56"/>
       <c r="C147" s="33" t="s">
         <v>120</v>
       </c>
@@ -9123,11 +9121,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="14.5" customHeight="1">
+    <row r="148" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A148" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B148" s="49"/>
+      <c r="B148" s="56"/>
       <c r="C148" s="33" t="s">
         <v>146</v>
       </c>
@@ -9168,11 +9166,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="14.5" customHeight="1">
+    <row r="149" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A149" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B149" s="49"/>
+      <c r="B149" s="56"/>
       <c r="C149" s="33" t="s">
         <v>116</v>
       </c>
@@ -9213,11 +9211,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="14.5" customHeight="1">
+    <row r="150" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A150" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B150" s="49"/>
+      <c r="B150" s="56"/>
       <c r="C150" s="33" t="s">
         <v>147</v>
       </c>
@@ -9258,11 +9256,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="14.5" customHeight="1">
+    <row r="151" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A151" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B151" s="49"/>
+      <c r="B151" s="56"/>
       <c r="C151" s="33" t="s">
         <v>148</v>
       </c>
@@ -9303,11 +9301,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="14.5" customHeight="1">
+    <row r="152" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A152" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B152" s="49"/>
+      <c r="B152" s="56"/>
       <c r="C152" s="33" t="s">
         <v>149</v>
       </c>
@@ -9348,11 +9346,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="14.5" customHeight="1">
+    <row r="153" spans="1:12" ht="14.5" hidden="1" customHeight="1">
       <c r="A153" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B153" s="49"/>
+      <c r="B153" s="56"/>
       <c r="C153" s="33" t="s">
         <v>150</v>
       </c>
@@ -9393,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
+    <row r="154" spans="1:12" ht="14.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A154" s="42" t="s">
         <v>136</v>
       </c>
@@ -9489,7 +9487,7 @@
       <c r="A156" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B156" s="49"/>
+      <c r="B156" s="56"/>
       <c r="C156" s="33" t="s">
         <v>154</v>
       </c>
@@ -9534,7 +9532,7 @@
       <c r="A157" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B157" s="49"/>
+      <c r="B157" s="56"/>
       <c r="C157" s="33" t="s">
         <v>155</v>
       </c>
@@ -9579,7 +9577,7 @@
       <c r="A158" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B158" s="49"/>
+      <c r="B158" s="56"/>
       <c r="C158" s="33" t="s">
         <v>156</v>
       </c>
@@ -9624,7 +9622,7 @@
       <c r="A159" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B159" s="49"/>
+      <c r="B159" s="56"/>
       <c r="C159" s="33" t="s">
         <v>157</v>
       </c>
@@ -9669,7 +9667,7 @@
       <c r="A160" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B160" s="49"/>
+      <c r="B160" s="56"/>
       <c r="C160" s="33" t="s">
         <v>158</v>
       </c>
@@ -9714,7 +9712,7 @@
       <c r="A161" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B161" s="49"/>
+      <c r="B161" s="56"/>
       <c r="C161" s="33" t="s">
         <v>159</v>
       </c>
@@ -9759,7 +9757,7 @@
       <c r="A162" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B162" s="49"/>
+      <c r="B162" s="56"/>
       <c r="C162" s="33" t="s">
         <v>160</v>
       </c>
@@ -9804,7 +9802,7 @@
       <c r="A163" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B163" s="49"/>
+      <c r="B163" s="56"/>
       <c r="C163" s="33" t="s">
         <v>161</v>
       </c>
@@ -9849,7 +9847,7 @@
       <c r="A164" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B164" s="49"/>
+      <c r="B164" s="56"/>
       <c r="C164" s="33" t="s">
         <v>162</v>
       </c>
@@ -9894,7 +9892,7 @@
       <c r="A165" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B165" s="49"/>
+      <c r="B165" s="56"/>
       <c r="C165" s="33" t="s">
         <v>163</v>
       </c>
@@ -9939,7 +9937,7 @@
       <c r="A166" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B166" s="49"/>
+      <c r="B166" s="56"/>
       <c r="C166" s="33" t="s">
         <v>164</v>
       </c>
@@ -9984,7 +9982,7 @@
       <c r="A167" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B167" s="49"/>
+      <c r="B167" s="56"/>
       <c r="C167" s="33" t="s">
         <v>165</v>
       </c>
@@ -10029,7 +10027,7 @@
       <c r="A168" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B168" s="49"/>
+      <c r="B168" s="56"/>
       <c r="C168" s="33" t="s">
         <v>166</v>
       </c>
@@ -10074,7 +10072,7 @@
       <c r="A169" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B169" s="49"/>
+      <c r="B169" s="56"/>
       <c r="C169" s="33" t="s">
         <v>167</v>
       </c>
@@ -10119,7 +10117,7 @@
       <c r="A170" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B170" s="49"/>
+      <c r="B170" s="56"/>
       <c r="C170" s="33" t="s">
         <v>168</v>
       </c>
@@ -10164,7 +10162,7 @@
       <c r="A171" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B171" s="49"/>
+      <c r="B171" s="56"/>
       <c r="C171" s="33" t="s">
         <v>169</v>
       </c>
@@ -10209,7 +10207,7 @@
       <c r="A172" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B172" s="49"/>
+      <c r="B172" s="56"/>
       <c r="C172" s="33" t="s">
         <v>170</v>
       </c>
@@ -10254,7 +10252,7 @@
       <c r="A173" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B173" s="49"/>
+      <c r="B173" s="56"/>
       <c r="C173" s="33" t="s">
         <v>171</v>
       </c>
@@ -10299,7 +10297,7 @@
       <c r="A174" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B174" s="49"/>
+      <c r="B174" s="56"/>
       <c r="C174" s="33" t="s">
         <v>172</v>
       </c>
@@ -10344,7 +10342,7 @@
       <c r="A175" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B175" s="49"/>
+      <c r="B175" s="56"/>
       <c r="C175" s="33" t="s">
         <v>173</v>
       </c>
@@ -10389,7 +10387,7 @@
       <c r="A176" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B176" s="49"/>
+      <c r="B176" s="56"/>
       <c r="C176" s="33" t="s">
         <v>174</v>
       </c>
@@ -10434,7 +10432,7 @@
       <c r="A177" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B177" s="49"/>
+      <c r="B177" s="56"/>
       <c r="C177" s="33" t="s">
         <v>175</v>
       </c>
@@ -10479,7 +10477,7 @@
       <c r="A178" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="B178" s="49"/>
+      <c r="B178" s="56"/>
       <c r="C178" s="33" t="s">
         <v>176</v>
       </c>
@@ -10616,7 +10614,7 @@
       <c r="A181" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B181" s="49"/>
+      <c r="B181" s="56"/>
       <c r="C181" s="33" t="s">
         <v>179</v>
       </c>
@@ -10661,7 +10659,7 @@
       <c r="A182" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B182" s="49"/>
+      <c r="B182" s="56"/>
       <c r="C182" s="33" t="s">
         <v>180</v>
       </c>
@@ -10706,7 +10704,7 @@
       <c r="A183" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B183" s="49"/>
+      <c r="B183" s="56"/>
       <c r="C183" s="33" t="s">
         <v>181</v>
       </c>
@@ -10751,7 +10749,7 @@
       <c r="A184" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B184" s="49"/>
+      <c r="B184" s="56"/>
       <c r="C184" s="33" t="s">
         <v>182</v>
       </c>
@@ -10796,7 +10794,7 @@
       <c r="A185" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B185" s="49"/>
+      <c r="B185" s="56"/>
       <c r="C185" s="33" t="s">
         <v>183</v>
       </c>
@@ -10841,7 +10839,7 @@
       <c r="A186" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B186" s="49"/>
+      <c r="B186" s="56"/>
       <c r="C186" s="33" t="s">
         <v>184</v>
       </c>
@@ -10886,7 +10884,7 @@
       <c r="A187" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B187" s="49"/>
+      <c r="B187" s="56"/>
       <c r="C187" s="33" t="s">
         <v>185</v>
       </c>
@@ -10931,7 +10929,7 @@
       <c r="A188" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B188" s="49"/>
+      <c r="B188" s="56"/>
       <c r="C188" s="33" t="s">
         <v>186</v>
       </c>
@@ -10976,7 +10974,7 @@
       <c r="A189" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B189" s="49"/>
+      <c r="B189" s="56"/>
       <c r="C189" s="33" t="s">
         <v>187</v>
       </c>
@@ -11021,7 +11019,7 @@
       <c r="A190" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B190" s="49"/>
+      <c r="B190" s="56"/>
       <c r="C190" s="33" t="s">
         <v>188</v>
       </c>
@@ -11066,7 +11064,7 @@
       <c r="A191" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B191" s="49"/>
+      <c r="B191" s="56"/>
       <c r="C191" s="33" t="s">
         <v>189</v>
       </c>
@@ -11111,7 +11109,7 @@
       <c r="A192" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B192" s="49"/>
+      <c r="B192" s="56"/>
       <c r="C192" s="33" t="s">
         <v>190</v>
       </c>
@@ -11156,7 +11154,7 @@
       <c r="A193" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B193" s="49"/>
+      <c r="B193" s="56"/>
       <c r="C193" s="33" t="s">
         <v>191</v>
       </c>
@@ -11201,7 +11199,7 @@
       <c r="A194" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B194" s="49"/>
+      <c r="B194" s="56"/>
       <c r="C194" s="33" t="s">
         <v>192</v>
       </c>
@@ -11246,7 +11244,7 @@
       <c r="A195" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B195" s="49"/>
+      <c r="B195" s="56"/>
       <c r="C195" s="33" t="s">
         <v>193</v>
       </c>
@@ -11291,7 +11289,7 @@
       <c r="A196" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B196" s="49"/>
+      <c r="B196" s="56"/>
       <c r="C196" s="33" t="s">
         <v>194</v>
       </c>
@@ -11336,7 +11334,7 @@
       <c r="A197" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B197" s="49"/>
+      <c r="B197" s="56"/>
       <c r="C197" s="33" t="s">
         <v>195</v>
       </c>
@@ -11381,7 +11379,7 @@
       <c r="A198" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B198" s="49"/>
+      <c r="B198" s="56"/>
       <c r="C198" s="33" t="s">
         <v>196</v>
       </c>
@@ -11426,7 +11424,7 @@
       <c r="A199" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B199" s="49"/>
+      <c r="B199" s="56"/>
       <c r="C199" s="33" t="s">
         <v>197</v>
       </c>
@@ -11471,7 +11469,7 @@
       <c r="A200" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B200" s="49"/>
+      <c r="B200" s="56"/>
       <c r="C200" s="33" t="s">
         <v>198</v>
       </c>
@@ -11516,7 +11514,7 @@
       <c r="A201" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B201" s="49"/>
+      <c r="B201" s="56"/>
       <c r="C201" s="33" t="s">
         <v>199</v>
       </c>
@@ -11561,7 +11559,7 @@
       <c r="A202" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B202" s="49"/>
+      <c r="B202" s="56"/>
       <c r="C202" s="33" t="s">
         <v>200</v>
       </c>
@@ -11606,7 +11604,7 @@
       <c r="A203" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B203" s="49"/>
+      <c r="B203" s="56"/>
       <c r="C203" s="33" t="s">
         <v>201</v>
       </c>
@@ -11651,7 +11649,7 @@
       <c r="A204" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B204" s="49"/>
+      <c r="B204" s="56"/>
       <c r="C204" s="33" t="s">
         <v>202</v>
       </c>
@@ -11696,7 +11694,7 @@
       <c r="A205" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B205" s="49"/>
+      <c r="B205" s="56"/>
       <c r="C205" s="33" t="s">
         <v>203</v>
       </c>
@@ -11741,7 +11739,7 @@
       <c r="A206" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B206" s="49"/>
+      <c r="B206" s="56"/>
       <c r="C206" s="33" t="s">
         <v>204</v>
       </c>
@@ -11786,7 +11784,7 @@
       <c r="A207" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B207" s="49"/>
+      <c r="B207" s="56"/>
       <c r="C207" s="33" t="s">
         <v>85</v>
       </c>
@@ -11831,7 +11829,7 @@
       <c r="A208" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B208" s="49"/>
+      <c r="B208" s="56"/>
       <c r="C208" s="33" t="s">
         <v>205</v>
       </c>
@@ -11876,7 +11874,7 @@
       <c r="A209" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B209" s="49"/>
+      <c r="B209" s="56"/>
       <c r="C209" s="33" t="s">
         <v>206</v>
       </c>
@@ -11921,7 +11919,7 @@
       <c r="A210" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B210" s="49"/>
+      <c r="B210" s="56"/>
       <c r="C210" s="33" t="s">
         <v>207</v>
       </c>
@@ -11966,7 +11964,7 @@
       <c r="A211" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B211" s="49"/>
+      <c r="B211" s="56"/>
       <c r="C211" s="33" t="s">
         <v>208</v>
       </c>
@@ -12011,7 +12009,7 @@
       <c r="A212" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B212" s="49"/>
+      <c r="B212" s="56"/>
       <c r="C212" s="33" t="s">
         <v>209</v>
       </c>
@@ -12056,7 +12054,7 @@
       <c r="A213" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="B213" s="49"/>
+      <c r="B213" s="56"/>
       <c r="C213" s="33" t="s">
         <v>210</v>
       </c>
@@ -12209,22 +12207,22 @@
     </row>
     <row r="220" spans="1:12" s="9" customFormat="1" ht="14.5" customHeight="1" thickBot="1">
       <c r="A220" s="45"/>
-      <c r="B220" s="64" t="s">
+      <c r="B220" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="C220" s="65"/>
-      <c r="D220" s="65"/>
-      <c r="E220" s="65"/>
-      <c r="F220" s="65"/>
-      <c r="G220" s="65"/>
-      <c r="H220" s="65"/>
-      <c r="I220" s="65"/>
-      <c r="J220" s="65"/>
-      <c r="K220" s="65"/>
-      <c r="L220" s="65"/>
+      <c r="C220" s="54"/>
+      <c r="D220" s="54"/>
+      <c r="E220" s="54"/>
+      <c r="F220" s="54"/>
+      <c r="G220" s="54"/>
+      <c r="H220" s="54"/>
+      <c r="I220" s="54"/>
+      <c r="J220" s="54"/>
+      <c r="K220" s="54"/>
+      <c r="L220" s="54"/>
     </row>
     <row r="221" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B221" s="67" t="s">
+      <c r="B221" s="61" t="s">
         <v>4</v>
       </c>
       <c r="C221" s="13" t="s">
@@ -12268,7 +12266,7 @@
       </c>
     </row>
     <row r="222" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B222" s="52"/>
+      <c r="B222" s="51"/>
       <c r="C222" s="15" t="s">
         <v>6</v>
       </c>
@@ -12310,7 +12308,7 @@
       </c>
     </row>
     <row r="223" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B223" s="53"/>
+      <c r="B223" s="52"/>
       <c r="C223" s="15" t="s">
         <v>7</v>
       </c>
@@ -12352,7 +12350,7 @@
       </c>
     </row>
     <row r="224" spans="1:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B224" s="51" t="s">
+      <c r="B224" s="50" t="s">
         <v>8</v>
       </c>
       <c r="C224" s="16" t="s">
@@ -12396,7 +12394,7 @@
       </c>
     </row>
     <row r="225" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B225" s="52"/>
+      <c r="B225" s="51"/>
       <c r="C225" s="18" t="s">
         <v>10</v>
       </c>
@@ -12438,7 +12436,7 @@
       </c>
     </row>
     <row r="226" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B226" s="52"/>
+      <c r="B226" s="51"/>
       <c r="C226" s="18" t="s">
         <v>11</v>
       </c>
@@ -12480,7 +12478,7 @@
       </c>
     </row>
     <row r="227" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B227" s="52"/>
+      <c r="B227" s="51"/>
       <c r="C227" s="18" t="s">
         <v>12</v>
       </c>
@@ -12522,7 +12520,7 @@
       </c>
     </row>
     <row r="228" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B228" s="52"/>
+      <c r="B228" s="51"/>
       <c r="C228" s="18" t="s">
         <v>13</v>
       </c>
@@ -12564,7 +12562,7 @@
       </c>
     </row>
     <row r="229" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B229" s="52"/>
+      <c r="B229" s="51"/>
       <c r="C229" s="18" t="s">
         <v>14</v>
       </c>
@@ -12606,7 +12604,7 @@
       </c>
     </row>
     <row r="230" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B230" s="52"/>
+      <c r="B230" s="51"/>
       <c r="C230" s="18" t="s">
         <v>15</v>
       </c>
@@ -12648,7 +12646,7 @@
       </c>
     </row>
     <row r="231" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B231" s="53"/>
+      <c r="B231" s="52"/>
       <c r="C231" s="18" t="s">
         <v>16</v>
       </c>
@@ -12690,7 +12688,7 @@
       </c>
     </row>
     <row r="232" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B232" s="56" t="s">
+      <c r="B232" s="68" t="s">
         <v>17</v>
       </c>
       <c r="C232" s="13" t="s">
@@ -12734,7 +12732,7 @@
       </c>
     </row>
     <row r="233" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B233" s="52"/>
+      <c r="B233" s="51"/>
       <c r="C233" s="15" t="s">
         <v>19</v>
       </c>
@@ -12776,7 +12774,7 @@
       </c>
     </row>
     <row r="234" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B234" s="52"/>
+      <c r="B234" s="51"/>
       <c r="C234" s="15" t="s">
         <v>20</v>
       </c>
@@ -12818,7 +12816,7 @@
       </c>
     </row>
     <row r="235" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B235" s="52"/>
+      <c r="B235" s="51"/>
       <c r="C235" s="15" t="s">
         <v>21</v>
       </c>
@@ -12860,7 +12858,7 @@
       </c>
     </row>
     <row r="236" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B236" s="52"/>
+      <c r="B236" s="51"/>
       <c r="C236" s="15" t="s">
         <v>22</v>
       </c>
@@ -12902,7 +12900,7 @@
       </c>
     </row>
     <row r="237" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B237" s="52"/>
+      <c r="B237" s="51"/>
       <c r="C237" s="15" t="s">
         <v>23</v>
       </c>
@@ -12944,7 +12942,7 @@
       </c>
     </row>
     <row r="238" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B238" s="53"/>
+      <c r="B238" s="52"/>
       <c r="C238" s="15" t="s">
         <v>24</v>
       </c>
@@ -12986,7 +12984,7 @@
       </c>
     </row>
     <row r="239" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B239" s="60" t="s">
+      <c r="B239" s="70" t="s">
         <v>25</v>
       </c>
       <c r="C239" s="20">
@@ -13030,7 +13028,7 @@
       </c>
     </row>
     <row r="240" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B240" s="52"/>
+      <c r="B240" s="51"/>
       <c r="C240" s="18">
         <v>2</v>
       </c>
@@ -13072,7 +13070,7 @@
       </c>
     </row>
     <row r="241" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B241" s="52"/>
+      <c r="B241" s="51"/>
       <c r="C241" s="18">
         <v>3</v>
       </c>
@@ -13114,7 +13112,7 @@
       </c>
     </row>
     <row r="242" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B242" s="52"/>
+      <c r="B242" s="51"/>
       <c r="C242" s="18">
         <v>4</v>
       </c>
@@ -13156,7 +13154,7 @@
       </c>
     </row>
     <row r="243" spans="2:12" ht="15" customHeight="1">
-      <c r="B243" s="52"/>
+      <c r="B243" s="51"/>
       <c r="C243" s="18">
         <v>5</v>
       </c>
@@ -13198,7 +13196,7 @@
       </c>
     </row>
     <row r="244" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B244" s="53"/>
+      <c r="B244" s="52"/>
       <c r="C244" s="18" t="s">
         <v>26</v>
       </c>
@@ -13240,7 +13238,7 @@
       </c>
     </row>
     <row r="245" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B245" s="51" t="s">
+      <c r="B245" s="50" t="s">
         <v>27</v>
       </c>
       <c r="C245" s="13" t="s">
@@ -13284,7 +13282,7 @@
       </c>
     </row>
     <row r="246" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B246" s="52"/>
+      <c r="B246" s="51"/>
       <c r="C246" s="15" t="s">
         <v>29</v>
       </c>
@@ -13326,7 +13324,7 @@
       </c>
     </row>
     <row r="247" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B247" s="52"/>
+      <c r="B247" s="51"/>
       <c r="C247" s="15" t="s">
         <v>30</v>
       </c>
@@ -13368,7 +13366,7 @@
       </c>
     </row>
     <row r="248" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B248" s="52"/>
+      <c r="B248" s="51"/>
       <c r="C248" s="15" t="s">
         <v>31</v>
       </c>
@@ -13410,7 +13408,7 @@
       </c>
     </row>
     <row r="249" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B249" s="53"/>
+      <c r="B249" s="52"/>
       <c r="C249" s="15" t="s">
         <v>32</v>
       </c>
@@ -13452,7 +13450,7 @@
       </c>
     </row>
     <row r="250" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B250" s="51" t="s">
+      <c r="B250" s="50" t="s">
         <v>33</v>
       </c>
       <c r="C250" s="20" t="s">
@@ -13496,7 +13494,7 @@
       </c>
     </row>
     <row r="251" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B251" s="52"/>
+      <c r="B251" s="51"/>
       <c r="C251" s="18" t="s">
         <v>35</v>
       </c>
@@ -13538,7 +13536,7 @@
       </c>
     </row>
     <row r="252" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B252" s="52"/>
+      <c r="B252" s="51"/>
       <c r="C252" s="18" t="s">
         <v>36</v>
       </c>
@@ -13580,7 +13578,7 @@
       </c>
     </row>
     <row r="253" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B253" s="53"/>
+      <c r="B253" s="52"/>
       <c r="C253" s="18" t="s">
         <v>37</v>
       </c>
@@ -13622,7 +13620,7 @@
       </c>
     </row>
     <row r="254" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B254" s="51" t="s">
+      <c r="B254" s="50" t="s">
         <v>38</v>
       </c>
       <c r="C254" s="13" t="s">
@@ -13666,7 +13664,7 @@
       </c>
     </row>
     <row r="255" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B255" s="52"/>
+      <c r="B255" s="51"/>
       <c r="C255" s="15" t="s">
         <v>40</v>
       </c>
@@ -13708,7 +13706,7 @@
       </c>
     </row>
     <row r="256" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B256" s="52"/>
+      <c r="B256" s="51"/>
       <c r="C256" s="15" t="s">
         <v>41</v>
       </c>
@@ -13750,7 +13748,7 @@
       </c>
     </row>
     <row r="257" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B257" s="52"/>
+      <c r="B257" s="51"/>
       <c r="C257" s="15" t="s">
         <v>42</v>
       </c>
@@ -13792,7 +13790,7 @@
       </c>
     </row>
     <row r="258" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B258" s="52"/>
+      <c r="B258" s="51"/>
       <c r="C258" s="15" t="s">
         <v>43</v>
       </c>
@@ -13834,7 +13832,7 @@
       </c>
     </row>
     <row r="259" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B259" s="53"/>
+      <c r="B259" s="52"/>
       <c r="C259" s="15" t="s">
         <v>44</v>
       </c>
@@ -13876,7 +13874,7 @@
       </c>
     </row>
     <row r="260" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B260" s="51" t="s">
+      <c r="B260" s="50" t="s">
         <v>45</v>
       </c>
       <c r="C260" s="22" t="s">
@@ -13920,7 +13918,7 @@
       </c>
     </row>
     <row r="261" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B261" s="52"/>
+      <c r="B261" s="51"/>
       <c r="C261" s="29" t="s">
         <v>35</v>
       </c>
@@ -13962,7 +13960,7 @@
       </c>
     </row>
     <row r="262" spans="2:12" ht="14.5" customHeight="1">
-      <c r="B262" s="52"/>
+      <c r="B262" s="51"/>
       <c r="C262" s="29" t="s">
         <v>36</v>
       </c>
@@ -14004,7 +14002,7 @@
       </c>
     </row>
     <row r="263" spans="2:12" ht="14.5" customHeight="1" thickBot="1">
-      <c r="B263" s="53"/>
+      <c r="B263" s="52"/>
       <c r="C263" s="30" t="s">
         <v>37</v>
       </c>
@@ -14384,21 +14382,7 @@
     <row r="280" ht="17" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B224:B231"/>
-    <mergeCell ref="B220:L220"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="B136:B154"/>
-    <mergeCell ref="B39:B44"/>
-    <mergeCell ref="B129:B135"/>
-    <mergeCell ref="B49:B57"/>
-    <mergeCell ref="B221:B223"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B76:B86"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B180:B214"/>
+    <mergeCell ref="B155:B179"/>
     <mergeCell ref="B245:B249"/>
     <mergeCell ref="B87:B91"/>
     <mergeCell ref="B6:B8"/>
@@ -14415,8 +14399,22 @@
     <mergeCell ref="B250:B253"/>
     <mergeCell ref="B58:B67"/>
     <mergeCell ref="B239:B244"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B224:B231"/>
+    <mergeCell ref="B220:L220"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="B136:B154"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="B129:B135"/>
+    <mergeCell ref="B49:B57"/>
+    <mergeCell ref="B221:B223"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B76:B86"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B180:B214"/>
     <mergeCell ref="B103:B110"/>
-    <mergeCell ref="B155:B179"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D10:D16">
